--- a/EXCEL/Data/løn_data/løndele_ialt.xlsx
+++ b/EXCEL/Data/løn_data/løndele_ialt.xlsx
@@ -97,7 +97,7 @@
     <t>Datasæt 02 2010</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 14.44.46</t>
+    <t>Kørsel 10.4.2026 10.34.30</t>
   </si>
   <si>
     <t/>

--- a/EXCEL/Data/løn_data/løndele_ialt.xlsx
+++ b/EXCEL/Data/løn_data/løndele_ialt.xlsx
@@ -97,7 +97,7 @@
     <t>Datasæt 02 2010</t>
   </si>
   <si>
-    <t>Kørsel 10.4.2026 10.34.30</t>
+    <t>Kørsel 14.4.2026 12.28.04</t>
   </si>
   <si>
     <t/>
